--- a/03_Outputs/all/01_TablasDescriptivas/idx8_demografica_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx8_demografica_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>7.557779220174639</v>
+        <v>7.557779220174641</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.7721147031344663</v>
+        <v>0.7721147031344655</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.7083432915192764</v>
+        <v>0.708343291519277</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2700456885683111</v>
+        <v>0.2700456885683113</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.05343126198455189</v>
+        <v>0.05343126198455181</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.01550900241341687</v>
+        <v>0.01550900241341685</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.001223051637038991</v>
+        <v>0.001223051637038992</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.0003798721070015031</v>
+        <v>0.0003798721070015038</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.615944776885471E-05</v>
+        <v>5.61594477688543E-05</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>7.557779220174639</v>
+        <v>7.557779220174641</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>8.990447849536602</v>
+        <v>8.990447849536604</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>9.762562552671069</v>
+        <v>9.762562552671071</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>10.47090584419034</v>
+        <v>10.47090584419035</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>10.92940065241022</v>
+        <v>10.92940065241023</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>10.99834091680819</v>
+        <v>10.9983409168082</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>10.99956396844523</v>
+        <v>10.99956396844524</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>10.99994384055223</v>
+        <v>10.99994384055224</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>11.00000000000001</v>
       </c>
       <c r="C23">
         <v>11</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>13.02426026692694</v>
+        <v>13.02426026692693</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>7.019224573949691</v>
+        <v>7.019224573949683</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>6.439484468357056</v>
+        <v>6.439484468357061</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>2.454960805166464</v>
+        <v>2.454960805166465</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.4857387453141079</v>
+        <v>0.4857387453141071</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.1409909310310624</v>
+        <v>0.1409909310310622</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.011118651245809</v>
+        <v>0.01111865124580902</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.003453382790922754</v>
+        <v>0.00345338279092276</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.0005105404342623154</v>
+        <v>0.0005105404342623116</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>81.73134408669635</v>
+        <v>81.73134408669637</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>95.1900531290031</v>
+        <v>95.19005312900312</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>97.64501393416957</v>
+        <v>97.64501393416958</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>99.84392649449792</v>
+        <v>99.84392649449795</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>99.98491742552899</v>
+        <v>99.98491742552901</v>
       </c>
       <c r="C42">
         <v>8</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>99.9960360767748</v>
+        <v>99.99603607677481</v>
       </c>
       <c r="C43">
         <v>9</v>
